--- a/input/mixed_complex.xlsx
+++ b/input/mixed_complex.xlsx
@@ -13,9 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="マスタ" sheetId="5" state="hidden" r:id="rId5"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'機能一覧'!$A$1:$E$5</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -861,7 +859,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E5"/>
   <dataValidations count="1">
     <dataValidation sqref="C2:C20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"画面,帳票,バッチ,API"</formula1>
